--- a/output/pdf_financials_xlsx/MY.xlsx
+++ b/output/pdf_financials_xlsx/MY.xlsx
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.443748</v>
+        <v>0.334583</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.154919</v>
+        <v>0.107103</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>1.352432</v>
@@ -3650,7 +3650,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.109165</v>
       </c>

--- a/output/pdf_financials_xlsx/MY.xlsx
+++ b/output/pdf_financials_xlsx/MY.xlsx
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.767884</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002568</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.767884</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002568</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.767941</v>
+        <v>5.7e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.002627</v>
+        <v>5.9e-05</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>5.9e-05</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
